--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92571087975</v>
+        <v>46157.93107773633</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93107773633</v>
+        <v>46157.93177720427</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93177720427</v>
+        <v>46157.93402599164</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93402599164</v>
+        <v>46157.93720608835</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93720608835</v>
+        <v>46158.28218695323</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28218695323</v>
+        <v>46158.29691928796</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29691928796</v>
+        <v>46158.29817758536</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29817758536</v>
+        <v>46158.3338966042</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3338966042</v>
+        <v>46158.36859497841</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/3. ИП МОМЗЕРОВ (масло для авто)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36859497841</v>
+        <v>46158.37290108517</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
